--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
   <si>
     <t>id</t>
   </si>
@@ -155,6 +155,12 @@
   </si>
   <si>
     <t>恭喜，您在【摇钱树】活动中中奖，由于您是VIP%s 中奖返利加成%s  额外将获得金币%s，请尽快领取以下返利!</t>
+  </si>
+  <si>
+    <t>上庄结束返还钻石</t>
+  </si>
+  <si>
+    <t>您在【%s】牌局在%s结束上庄，剩余现在已经返回游戏中的剩余上庄金额，请尽快领取！</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1122,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="3.75" style="3" customWidth="1"/>
@@ -1217,7 +1223,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F21" si="0">7*24*60*60</f>
+        <f t="shared" ref="F5:F22" si="0">7*24*60*60</f>
         <v>604800</v>
       </c>
       <c r="G5" s="3">
@@ -1657,6 +1663,33 @@
       </c>
       <c r="H21" s="3" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="3">
+        <v>39</v>
+      </c>
+      <c r="B22" s="3">
+        <v>11414</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="3">
+        <v>11008</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G22" s="3">
+        <v>11617</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
   <si>
     <t>id</t>
   </si>
@@ -67,7 +67,7 @@
     <t>系统</t>
   </si>
   <si>
-    <t>欢迎进入拉斯维加斯，祝您生活愉快</t>
+    <t>欢迎来到【Jackpot Online-Casino mogul】棋牌游戏，您将在这里体验到特别的快乐，祝您游戏愉快，天天赢大奖，早日实现财富自由！</t>
   </si>
   <si>
     <t>自动续时中断通知</t>
@@ -161,6 +161,12 @@
   </si>
   <si>
     <t>您在【%s】牌局在%s结束上庄，剩余现在已经返回游戏中的剩余上庄金额，请尽快领取！</t>
+  </si>
+  <si>
+    <t>【积分大奖】进度奖励</t>
+  </si>
+  <si>
+    <t>您在【积分大奖】活动中还有积分进度奖励未领取，请尽快领取！</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="3.75" style="3" customWidth="1"/>
@@ -1223,7 +1229,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F22" si="0">7*24*60*60</f>
+        <f t="shared" ref="F5:F23" si="0">7*24*60*60</f>
         <v>604800</v>
       </c>
       <c r="G5" s="3">
@@ -1690,6 +1696,33 @@
       </c>
       <c r="H22" s="2" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="3">
+        <v>40</v>
+      </c>
+      <c r="B23" s="3">
+        <v>11415</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G23" s="3">
+        <v>11618</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="48">
   <si>
     <t>id</t>
   </si>
@@ -167,6 +167,12 @@
   </si>
   <si>
     <t>您在【积分大奖】活动中还有积分进度奖励未领取，请尽快领取！</t>
+  </si>
+  <si>
+    <t>【幸运夺宝】中奖奖励</t>
+  </si>
+  <si>
+    <t>恭喜您在【幸运夺宝】活动中中奖了，赢得以下奖励，请尽快领取！</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1134,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="3.75" style="3" customWidth="1"/>
@@ -1723,6 +1729,33 @@
       </c>
       <c r="H23" s="2" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="3">
+        <v>41</v>
+      </c>
+      <c r="B24" s="3">
+        <v>11416</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="3">
+        <v>11008</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="2">
+        <f>7*24*60*60</f>
+        <v>604800</v>
+      </c>
+      <c r="G24" s="3">
+        <v>11619</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
   <si>
     <t>id</t>
   </si>
@@ -173,6 +173,12 @@
   </si>
   <si>
     <t>恭喜您在【幸运夺宝】活动中中奖了，赢得以下奖励，请尽快领取！</t>
+  </si>
+  <si>
+    <t>【每日充值】进度礼包奖励</t>
+  </si>
+  <si>
+    <t>您在【每日充值】活动中达到了进度礼包的领取条件，【每日充值】重置后还有未领取的奖励，请尽快领取以下奖励！</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1140,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="3.75" style="3" customWidth="1"/>
@@ -1235,7 +1241,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F23" si="0">7*24*60*60</f>
+        <f t="shared" ref="F5:F25" si="0">7*24*60*60</f>
         <v>604800</v>
       </c>
       <c r="G5" s="3">
@@ -1748,7 +1754,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="2">
-        <f>7*24*60*60</f>
+        <f t="shared" si="0"/>
         <v>604800</v>
       </c>
       <c r="G24" s="3">
@@ -1756,6 +1762,33 @@
       </c>
       <c r="H24" s="3" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="3">
+        <v>42</v>
+      </c>
+      <c r="B25" s="3">
+        <v>11417</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="3">
+        <v>11008</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G25" s="3">
+        <v>11620</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="mail" sheetId="1" r:id="rId1"/>
@@ -82,10 +82,10 @@
     <t>积分大奖排行奖励-时段榜</t>
   </si>
   <si>
-    <t>您在【积分大奖】活动中【第d%期s%】的时段排行榜中获得第d%名，请尽快领取以下奖励!</t>
-  </si>
-  <si>
-    <t>您在【积分大奖】活动中【第d%期s%】的时段排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
+    <t>您在【积分大奖】活动中【第d%期】的日榜排行榜中获得第d%名，请尽快领取以下奖励!</t>
+  </si>
+  <si>
+    <t>您在【积分大奖】活动中【第d%期】的周榜排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
   </si>
   <si>
     <t>积分大奖排行奖励-月总榜</t>

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="mail" sheetId="1" r:id="rId1"/>
@@ -112,25 +112,25 @@
     <t>[ google绑定 ]奖励</t>
   </si>
   <si>
-    <t>您绑定了 Google账号，免费获得 1,400,000金币，请尽快领取金币奖励!</t>
+    <t>您绑定了 Google账号，免费获得 5,200金币，请尽快领取金币奖励!</t>
   </si>
   <si>
     <t>[ facebook绑定 ]奖励</t>
   </si>
   <si>
-    <t>您绑定了 facebook账号，免费获得 1,400,000金币，请尽快领取金币奖励!</t>
+    <t>您绑定了 facebook账号，免费获得 5,200金金币，请尽快领取金币奖励!</t>
   </si>
   <si>
     <t>[ 手机绑定 ]奖励</t>
   </si>
   <si>
-    <t>您绑定了 手机号码，免费获得 1,400,000金币，请尽快领取金币奖励!</t>
+    <t>您绑定了 手机号码，免费获得 5,200金金币，请尽快领取金币奖励!</t>
   </si>
   <si>
     <t>[ Apple绑定 ]奖励</t>
   </si>
   <si>
-    <t>您绑定了 Apple账号，免费获得 1,400,000金币，请尽快领取金币奖励!</t>
+    <t>您绑定了 Apple账号，免费获得 5,200金金币，请尽快领取金币奖励!</t>
   </si>
   <si>
     <t>房间销毁返还钻石</t>
@@ -1484,7 +1484,6 @@
         <v>11</v>
       </c>
       <c r="F14" s="2">
-        <f t="shared" si="0"/>
         <v>604800</v>
       </c>
       <c r="G14" s="2">
@@ -1511,7 +1510,6 @@
         <v>11</v>
       </c>
       <c r="F15" s="2">
-        <f t="shared" si="0"/>
         <v>604800</v>
       </c>
       <c r="G15" s="3">
@@ -1538,7 +1536,6 @@
         <v>11</v>
       </c>
       <c r="F16" s="2">
-        <f t="shared" si="0"/>
         <v>604800</v>
       </c>
       <c r="G16" s="3">
@@ -1565,7 +1562,6 @@
         <v>11</v>
       </c>
       <c r="F17" s="2">
-        <f t="shared" si="0"/>
         <v>604800</v>
       </c>
       <c r="G17" s="3">

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -82,10 +82,10 @@
     <t>积分大奖排行奖励-时段榜</t>
   </si>
   <si>
-    <t>您在【积分大奖】活动中【第d%期s%】的时段排行榜中获得第d%名，请尽快领取以下奖励!</t>
-  </si>
-  <si>
-    <t>您在【积分大奖】活动中【第d%期s%】的时段排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
+    <t>您在【积分大奖】活动中【第d%期】的日榜排行榜中获得第d%名，请尽快领取以下奖励!</t>
+  </si>
+  <si>
+    <t>您在【积分大奖】活动中【第d%期】的周榜排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
   </si>
   <si>
     <t>积分大奖排行奖励-月总榜</t>
@@ -112,25 +112,25 @@
     <t>[ google绑定 ]奖励</t>
   </si>
   <si>
-    <t>您绑定了 Google账号，免费获得 1,400,000金币，请尽快领取金币奖励!</t>
+    <t>您绑定了 Google账号，免费获得 5,200金币，请尽快领取金币奖励!</t>
   </si>
   <si>
     <t>[ facebook绑定 ]奖励</t>
   </si>
   <si>
-    <t>您绑定了 facebook账号，免费获得 1,400,000金币，请尽快领取金币奖励!</t>
+    <t>您绑定了 facebook账号，免费获得 5,200金金币，请尽快领取金币奖励!</t>
   </si>
   <si>
     <t>[ 手机绑定 ]奖励</t>
   </si>
   <si>
-    <t>您绑定了 手机号码，免费获得 1,400,000金币，请尽快领取金币奖励!</t>
+    <t>您绑定了 手机号码，免费获得 5,200金金币，请尽快领取金币奖励!</t>
   </si>
   <si>
     <t>[ Apple绑定 ]奖励</t>
   </si>
   <si>
-    <t>您绑定了 Apple账号，免费获得 1,400,000金币，请尽快领取金币奖励!</t>
+    <t>您绑定了 Apple账号，免费获得 5,200金金币，请尽快领取金币奖励!</t>
   </si>
   <si>
     <t>房间销毁返还钻石</t>
@@ -1484,7 +1484,6 @@
         <v>11</v>
       </c>
       <c r="F14" s="2">
-        <f t="shared" si="0"/>
         <v>604800</v>
       </c>
       <c r="G14" s="2">
@@ -1511,7 +1510,6 @@
         <v>11</v>
       </c>
       <c r="F15" s="2">
-        <f t="shared" si="0"/>
         <v>604800</v>
       </c>
       <c r="G15" s="3">
@@ -1538,7 +1536,6 @@
         <v>11</v>
       </c>
       <c r="F16" s="2">
-        <f t="shared" si="0"/>
         <v>604800</v>
       </c>
       <c r="G16" s="3">
@@ -1565,7 +1562,6 @@
         <v>11</v>
       </c>
       <c r="F17" s="2">
-        <f t="shared" si="0"/>
         <v>604800</v>
       </c>
       <c r="G17" s="3">

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
   <si>
     <t>id</t>
   </si>
@@ -79,10 +79,13 @@
     <t>您的【{0}】牌局在{1}，由于牌局自动扣费失败，已中断自动续时功能</t>
   </si>
   <si>
-    <t>积分大奖排行奖励-时段榜</t>
+    <t>积分大奖排行奖励-每日榜</t>
   </si>
   <si>
     <t>您在【积分大奖】活动中【第d%期】的日榜排行榜中获得第d%名，请尽快领取以下奖励!</t>
+  </si>
+  <si>
+    <t>积分大奖排行奖励-每周榜</t>
   </si>
   <si>
     <t>您在【积分大奖】活动中【第d%期】的周榜排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
@@ -1340,7 +1343,7 @@
         <v>11403</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" s="2">
         <v>11008</v>
@@ -1356,7 +1359,7 @@
         <v>11604</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:8">
@@ -1367,7 +1370,7 @@
         <v>11403</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="2">
         <v>11008</v>
@@ -1383,7 +1386,7 @@
         <v>11605</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:8">
@@ -1394,7 +1397,7 @@
         <v>11403</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2">
         <v>11008</v>
@@ -1410,7 +1413,7 @@
         <v>11606</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:8">
@@ -1421,7 +1424,7 @@
         <v>11404</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="2">
         <v>11008</v>
@@ -1437,7 +1440,7 @@
         <v>11607</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:8">
@@ -1448,7 +1451,7 @@
         <v>11405</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2">
         <v>11008</v>
@@ -1464,7 +1467,7 @@
         <v>11608</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:8">
@@ -1475,7 +1478,7 @@
         <v>11406</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="2">
         <v>11008</v>
@@ -1490,7 +1493,7 @@
         <v>11609</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1501,7 +1504,7 @@
         <v>11407</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2">
         <v>11008</v>
@@ -1516,7 +1519,7 @@
         <v>11610</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1527,7 +1530,7 @@
         <v>11408</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" s="2">
         <v>11008</v>
@@ -1542,7 +1545,7 @@
         <v>11611</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1553,7 +1556,7 @@
         <v>11409</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" s="2">
         <v>11008</v>
@@ -1568,7 +1571,7 @@
         <v>11612</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1579,7 +1582,7 @@
         <v>11410</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" s="3">
         <v>11008</v>
@@ -1595,7 +1598,7 @@
         <v>11613</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1606,7 +1609,7 @@
         <v>11411</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D19" s="2">
         <v>11008</v>
@@ -1622,7 +1625,7 @@
         <v>11614</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1633,7 +1636,7 @@
         <v>11412</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D20" s="3">
         <v>11008</v>
@@ -1649,7 +1652,7 @@
         <v>11615</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1660,7 +1663,7 @@
         <v>11413</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D21" s="2">
         <v>11008</v>
@@ -1676,7 +1679,7 @@
         <v>11616</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1687,7 +1690,7 @@
         <v>11414</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D22" s="3">
         <v>11008</v>
@@ -1703,7 +1706,7 @@
         <v>11617</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1714,7 +1717,7 @@
         <v>11415</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D23" s="2">
         <v>11008</v>
@@ -1730,7 +1733,7 @@
         <v>11618</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1741,7 +1744,7 @@
         <v>11416</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" s="3">
         <v>11008</v>
@@ -1757,7 +1760,7 @@
         <v>11619</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1768,7 +1771,7 @@
         <v>11417</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D25" s="3">
         <v>11008</v>
@@ -1784,7 +1787,7 @@
         <v>11620</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="53">
   <si>
     <t>id</t>
   </si>
@@ -85,103 +85,109 @@
     <t>您在【积分大奖】活动中【第d%期】的日榜排行榜中获得第d%名，请尽快领取以下奖励!</t>
   </si>
   <si>
+    <t>您在【积分大奖】活动中【第d%期】的日榜排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
+  </si>
+  <si>
+    <t>积分大奖排行奖励-月总榜</t>
+  </si>
+  <si>
+    <t>您在【积分大奖】活动中【第d%期】的月排行榜中获得第d%名，请尽快领取以下奖励!</t>
+  </si>
+  <si>
+    <t>您在【积分大奖】活动中【第d%期】的月排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
+  </si>
+  <si>
+    <t>分享推广-周榜奖励结算发邮件</t>
+  </si>
+  <si>
+    <t>您在【分享推广】活动中周榜排名第d%名，请尽快领取以下奖励!</t>
+  </si>
+  <si>
+    <t>储钱罐-未领奖励到期发邮件</t>
+  </si>
+  <si>
+    <t>您在【储钱罐】活动中购买了一个储钱罐，储钱罐被重置后还有未领取的奖励，请尽快领取以下奖励!</t>
+  </si>
+  <si>
+    <t>[ google绑定 ]奖励</t>
+  </si>
+  <si>
+    <t>您绑定了 Google账号，免费获得 5,200金币，请尽快领取金币奖励!</t>
+  </si>
+  <si>
+    <t>[ facebook绑定 ]奖励</t>
+  </si>
+  <si>
+    <t>您绑定了 facebook账号，免费获得 5,200金金币，请尽快领取金币奖励!</t>
+  </si>
+  <si>
+    <t>[ 手机绑定 ]奖励</t>
+  </si>
+  <si>
+    <t>您绑定了 手机号码，免费获得 5,200金金币，请尽快领取金币奖励!</t>
+  </si>
+  <si>
+    <t>[ Apple绑定 ]奖励</t>
+  </si>
+  <si>
+    <t>您绑定了 Apple账号，免费获得 5,200金金币，请尽快领取金币奖励!</t>
+  </si>
+  <si>
+    <t>房间销毁返还钻石</t>
+  </si>
+  <si>
+    <t>您的【%s】牌局在%s被撤销，现在已经返回游戏中的底庄金额，请尽快领取！</t>
+  </si>
+  <si>
+    <t>[ VIP充值返利 ]金币</t>
+  </si>
+  <si>
+    <t>您在【商城-金币】充值$%s，由于您是VIP%s 充值返利加成%s 额外将获得金币%s ，请尽快领取以下返利!</t>
+  </si>
+  <si>
+    <t>[ VIP充值返利 ]钻石</t>
+  </si>
+  <si>
+    <t>您在【商城-钻石】充值$%s，由于您是VIP%s 充值返利加成%s 额外将获得钻石%s ，请尽快领取以下返利!</t>
+  </si>
+  <si>
+    <t>[ VIP充值返利 ]摇钱树</t>
+  </si>
+  <si>
+    <t>恭喜，您在【摇钱树】活动中中奖，由于您是VIP%s 中奖返利加成%s  额外将获得金币%s，请尽快领取以下返利!</t>
+  </si>
+  <si>
+    <t>上庄结束返还钻石</t>
+  </si>
+  <si>
+    <t>您在【%s】牌局在%s结束上庄，剩余现在已经返回游戏中的剩余上庄金额，请尽快领取！</t>
+  </si>
+  <si>
+    <t>【积分大奖】进度奖励</t>
+  </si>
+  <si>
+    <t>您在【积分大奖】活动中还有积分进度奖励未领取，请尽快领取！</t>
+  </si>
+  <si>
+    <t>【幸运夺宝】中奖奖励</t>
+  </si>
+  <si>
+    <t>恭喜您在【幸运夺宝】活动中中奖了，赢得以下奖励，请尽快领取！</t>
+  </si>
+  <si>
+    <t>【每日充值】进度礼包奖励</t>
+  </si>
+  <si>
+    <t>您在【每日充值】活动中达到了进度礼包的领取条件，【每日充值】重置后还有未领取的奖励，请尽快领取以下奖励！</t>
+  </si>
+  <si>
     <t>积分大奖排行奖励-每周榜</t>
   </si>
   <si>
+    <t>您在【积分大奖】活动中【第d%期】的周榜排行榜中获得第d%名，请尽快领取以下奖励!</t>
+  </si>
+  <si>
     <t>您在【积分大奖】活动中【第d%期】的周榜排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
-  </si>
-  <si>
-    <t>积分大奖排行奖励-月总榜</t>
-  </si>
-  <si>
-    <t>您在【积分大奖】活动中【第d%期】的月排行榜中获得第d%名，请尽快领取以下奖励!</t>
-  </si>
-  <si>
-    <t>您在【积分大奖】活动中【第d%期】的月排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
-  </si>
-  <si>
-    <t>分享推广-周榜奖励结算发邮件</t>
-  </si>
-  <si>
-    <t>您在【分享推广】活动中周榜排名第d%名，请尽快领取以下奖励!</t>
-  </si>
-  <si>
-    <t>储钱罐-未领奖励到期发邮件</t>
-  </si>
-  <si>
-    <t>您在【储钱罐】活动中购买了一个储钱罐，储钱罐被重置后还有未领取的奖励，请尽快领取以下奖励!</t>
-  </si>
-  <si>
-    <t>[ google绑定 ]奖励</t>
-  </si>
-  <si>
-    <t>您绑定了 Google账号，免费获得 5,200金币，请尽快领取金币奖励!</t>
-  </si>
-  <si>
-    <t>[ facebook绑定 ]奖励</t>
-  </si>
-  <si>
-    <t>您绑定了 facebook账号，免费获得 5,200金金币，请尽快领取金币奖励!</t>
-  </si>
-  <si>
-    <t>[ 手机绑定 ]奖励</t>
-  </si>
-  <si>
-    <t>您绑定了 手机号码，免费获得 5,200金金币，请尽快领取金币奖励!</t>
-  </si>
-  <si>
-    <t>[ Apple绑定 ]奖励</t>
-  </si>
-  <si>
-    <t>您绑定了 Apple账号，免费获得 5,200金金币，请尽快领取金币奖励!</t>
-  </si>
-  <si>
-    <t>房间销毁返还钻石</t>
-  </si>
-  <si>
-    <t>您的【%s】牌局在%s被撤销，现在已经返回游戏中的底庄金额，请尽快领取！</t>
-  </si>
-  <si>
-    <t>[ VIP充值返利 ]金币</t>
-  </si>
-  <si>
-    <t>您在【商城-金币】充值$%s，由于您是VIP%s 充值返利加成%s 额外将获得金币%s ，请尽快领取以下返利!</t>
-  </si>
-  <si>
-    <t>[ VIP充值返利 ]钻石</t>
-  </si>
-  <si>
-    <t>您在【商城-钻石】充值$%s，由于您是VIP%s 充值返利加成%s 额外将获得钻石%s ，请尽快领取以下返利!</t>
-  </si>
-  <si>
-    <t>[ VIP充值返利 ]摇钱树</t>
-  </si>
-  <si>
-    <t>恭喜，您在【摇钱树】活动中中奖，由于您是VIP%s 中奖返利加成%s  额外将获得金币%s，请尽快领取以下返利!</t>
-  </si>
-  <si>
-    <t>上庄结束返还钻石</t>
-  </si>
-  <si>
-    <t>您在【%s】牌局在%s结束上庄，剩余现在已经返回游戏中的剩余上庄金额，请尽快领取！</t>
-  </si>
-  <si>
-    <t>【积分大奖】进度奖励</t>
-  </si>
-  <si>
-    <t>您在【积分大奖】活动中还有积分进度奖励未领取，请尽快领取！</t>
-  </si>
-  <si>
-    <t>【幸运夺宝】中奖奖励</t>
-  </si>
-  <si>
-    <t>恭喜您在【幸运夺宝】活动中中奖了，赢得以下奖励，请尽快领取！</t>
-  </si>
-  <si>
-    <t>【每日充值】进度礼包奖励</t>
-  </si>
-  <si>
-    <t>您在【每日充值】活动中达到了进度礼包的领取条件，【每日充值】重置后还有未领取的奖励，请尽快领取以下奖励！</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="3.75" style="3" customWidth="1"/>
@@ -1244,7 +1250,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F25" si="0">7*24*60*60</f>
+        <f t="shared" ref="F5:F27" si="0">7*24*60*60</f>
         <v>604800</v>
       </c>
       <c r="G5" s="3">
@@ -1343,7 +1349,7 @@
         <v>11403</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2">
         <v>11008</v>
@@ -1359,7 +1365,7 @@
         <v>11604</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:8">
@@ -1370,7 +1376,7 @@
         <v>11403</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="2">
         <v>11008</v>
@@ -1386,7 +1392,7 @@
         <v>11605</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:8">
@@ -1397,7 +1403,7 @@
         <v>11403</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="2">
         <v>11008</v>
@@ -1413,7 +1419,7 @@
         <v>11606</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:8">
@@ -1424,7 +1430,7 @@
         <v>11404</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="2">
         <v>11008</v>
@@ -1440,7 +1446,7 @@
         <v>11607</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:8">
@@ -1451,7 +1457,7 @@
         <v>11405</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2">
         <v>11008</v>
@@ -1467,7 +1473,7 @@
         <v>11608</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:8">
@@ -1478,7 +1484,7 @@
         <v>11406</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2">
         <v>11008</v>
@@ -1493,7 +1499,7 @@
         <v>11609</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1504,7 +1510,7 @@
         <v>11407</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2">
         <v>11008</v>
@@ -1519,7 +1525,7 @@
         <v>11610</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1530,7 +1536,7 @@
         <v>11408</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" s="2">
         <v>11008</v>
@@ -1545,7 +1551,7 @@
         <v>11611</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1556,7 +1562,7 @@
         <v>11409</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" s="2">
         <v>11008</v>
@@ -1571,7 +1577,7 @@
         <v>11612</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1582,7 +1588,7 @@
         <v>11410</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" s="3">
         <v>11008</v>
@@ -1598,7 +1604,7 @@
         <v>11613</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1609,7 +1615,7 @@
         <v>11411</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" s="2">
         <v>11008</v>
@@ -1625,7 +1631,7 @@
         <v>11614</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1636,7 +1642,7 @@
         <v>11412</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D20" s="3">
         <v>11008</v>
@@ -1652,7 +1658,7 @@
         <v>11615</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1663,7 +1669,7 @@
         <v>11413</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D21" s="2">
         <v>11008</v>
@@ -1679,7 +1685,7 @@
         <v>11616</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1690,7 +1696,7 @@
         <v>11414</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D22" s="3">
         <v>11008</v>
@@ -1706,7 +1712,7 @@
         <v>11617</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1717,7 +1723,7 @@
         <v>11415</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D23" s="2">
         <v>11008</v>
@@ -1733,7 +1739,7 @@
         <v>11618</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1744,7 +1750,7 @@
         <v>11416</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" s="3">
         <v>11008</v>
@@ -1760,7 +1766,7 @@
         <v>11619</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1771,7 +1777,7 @@
         <v>11417</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" s="3">
         <v>11008</v>
@@ -1787,7 +1793,61 @@
         <v>11620</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="1:8">
+      <c r="A26" s="2">
+        <v>43</v>
+      </c>
+      <c r="B26" s="2">
+        <v>11403</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>50</v>
+      </c>
+      <c r="D26" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G26" s="2">
+        <v>11621</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:8">
+      <c r="A27" s="2">
+        <v>44</v>
+      </c>
+      <c r="B27" s="2">
+        <v>11403</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G27" s="2">
+        <v>11622</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
   <si>
     <t>id</t>
   </si>
@@ -79,13 +79,10 @@
     <t>您的【{0}】牌局在{1}，由于牌局自动扣费失败，已中断自动续时功能</t>
   </si>
   <si>
-    <t>积分大奖排行奖励-每日榜</t>
+    <t>积分大奖排行奖励-时段榜</t>
   </si>
   <si>
     <t>您在【积分大奖】活动中【第d%期】的日榜排行榜中获得第d%名，请尽快领取以下奖励!</t>
-  </si>
-  <si>
-    <t>积分大奖排行奖励-每周榜</t>
   </si>
   <si>
     <t>您在【积分大奖】活动中【第d%期】的周榜排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
@@ -1343,7 +1340,7 @@
         <v>11403</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2">
         <v>11008</v>
@@ -1359,7 +1356,7 @@
         <v>11604</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:8">
@@ -1370,7 +1367,7 @@
         <v>11403</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="2">
         <v>11008</v>
@@ -1386,7 +1383,7 @@
         <v>11605</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:8">
@@ -1397,7 +1394,7 @@
         <v>11403</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="2">
         <v>11008</v>
@@ -1413,7 +1410,7 @@
         <v>11606</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:8">
@@ -1424,7 +1421,7 @@
         <v>11404</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="2">
         <v>11008</v>
@@ -1440,7 +1437,7 @@
         <v>11607</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:8">
@@ -1451,7 +1448,7 @@
         <v>11405</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2">
         <v>11008</v>
@@ -1467,7 +1464,7 @@
         <v>11608</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:8">
@@ -1478,7 +1475,7 @@
         <v>11406</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2">
         <v>11008</v>
@@ -1493,7 +1490,7 @@
         <v>11609</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1504,7 +1501,7 @@
         <v>11407</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2">
         <v>11008</v>
@@ -1519,7 +1516,7 @@
         <v>11610</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1530,7 +1527,7 @@
         <v>11408</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" s="2">
         <v>11008</v>
@@ -1545,7 +1542,7 @@
         <v>11611</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1556,7 +1553,7 @@
         <v>11409</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" s="2">
         <v>11008</v>
@@ -1571,7 +1568,7 @@
         <v>11612</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1582,7 +1579,7 @@
         <v>11410</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" s="3">
         <v>11008</v>
@@ -1598,7 +1595,7 @@
         <v>11613</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1609,7 +1606,7 @@
         <v>11411</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" s="2">
         <v>11008</v>
@@ -1625,7 +1622,7 @@
         <v>11614</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1636,7 +1633,7 @@
         <v>11412</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D20" s="3">
         <v>11008</v>
@@ -1652,7 +1649,7 @@
         <v>11615</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1663,7 +1660,7 @@
         <v>11413</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D21" s="2">
         <v>11008</v>
@@ -1679,7 +1676,7 @@
         <v>11616</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1690,7 +1687,7 @@
         <v>11414</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D22" s="3">
         <v>11008</v>
@@ -1706,7 +1703,7 @@
         <v>11617</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1717,7 +1714,7 @@
         <v>11415</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D23" s="2">
         <v>11008</v>
@@ -1733,7 +1730,7 @@
         <v>11618</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1744,7 +1741,7 @@
         <v>11416</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" s="3">
         <v>11008</v>
@@ -1760,7 +1757,7 @@
         <v>11619</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1771,7 +1768,7 @@
         <v>11417</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" s="3">
         <v>11008</v>
@@ -1787,7 +1784,7 @@
         <v>11620</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="53">
   <si>
     <t>id</t>
   </si>
@@ -79,106 +79,115 @@
     <t>您的【{0}】牌局在{1}，由于牌局自动扣费失败，已中断自动续时功能</t>
   </si>
   <si>
-    <t>积分大奖排行奖励-时段榜</t>
+    <t>积分大奖排行奖励-每日榜</t>
   </si>
   <si>
     <t>您在【积分大奖】活动中【第d%期】的日榜排行榜中获得第d%名，请尽快领取以下奖励!</t>
   </si>
   <si>
+    <t>您在【积分大奖】活动中【第d%期】的日榜排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
+  </si>
+  <si>
+    <t>积分大奖排行奖励-月总榜</t>
+  </si>
+  <si>
+    <t>您在【积分大奖】活动中【第d%期】的月排行榜中获得第d%名，请尽快领取以下奖励!</t>
+  </si>
+  <si>
+    <t>您在【积分大奖】活动中【第d%期】的月排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
+  </si>
+  <si>
+    <t>分享推广-周榜奖励结算发邮件</t>
+  </si>
+  <si>
+    <t>您在【分享推广】活动中周榜排名第d%名，请尽快领取以下奖励!</t>
+  </si>
+  <si>
+    <t>储钱罐-未领奖励到期发邮件</t>
+  </si>
+  <si>
+    <t>您在【储钱罐】活动中购买了一个储钱罐，储钱罐被重置后还有未领取的奖励，请尽快领取以下奖励!</t>
+  </si>
+  <si>
+    <t>[ google绑定 ]奖励</t>
+  </si>
+  <si>
+    <t>您绑定了 Google账号，免费获得 5,200金币，请尽快领取金币奖励!</t>
+  </si>
+  <si>
+    <t>[ facebook绑定 ]奖励</t>
+  </si>
+  <si>
+    <t>您绑定了 facebook账号，免费获得 5,200金金币，请尽快领取金币奖励!</t>
+  </si>
+  <si>
+    <t>[ 手机绑定 ]奖励</t>
+  </si>
+  <si>
+    <t>您绑定了 手机号码，免费获得 5,200金金币，请尽快领取金币奖励!</t>
+  </si>
+  <si>
+    <t>[ Apple绑定 ]奖励</t>
+  </si>
+  <si>
+    <t>您绑定了 Apple账号，免费获得 5,200金金币，请尽快领取金币奖励!</t>
+  </si>
+  <si>
+    <t>房间销毁返还钻石</t>
+  </si>
+  <si>
+    <t>您的【%s】牌局在%s被撤销，现在已经返回游戏中的底庄金额，请尽快领取！</t>
+  </si>
+  <si>
+    <t>[ VIP充值返利 ]金币</t>
+  </si>
+  <si>
+    <t>您在【商城-金币】充值$%s，由于您是VIP%s 充值返利加成%s 额外将获得金币%s ，请尽快领取以下返利!</t>
+  </si>
+  <si>
+    <t>[ VIP充值返利 ]钻石</t>
+  </si>
+  <si>
+    <t>您在【商城-钻石】充值$%s，由于您是VIP%s 充值返利加成%s 额外将获得钻石%s ，请尽快领取以下返利!</t>
+  </si>
+  <si>
+    <t>[ VIP充值返利 ]摇钱树</t>
+  </si>
+  <si>
+    <t>恭喜，您在【摇钱树】活动中中奖，由于您是VIP%s 中奖返利加成%s  额外将获得金币%s，请尽快领取以下返利!</t>
+  </si>
+  <si>
+    <t>上庄结束返还钻石</t>
+  </si>
+  <si>
+    <t>您在【%s】牌局在%s结束上庄，剩余现在已经返回游戏中的剩余上庄金额，请尽快领取！</t>
+  </si>
+  <si>
+    <t>【积分大奖】进度奖励</t>
+  </si>
+  <si>
+    <t>您在【积分大奖】活动中还有积分进度奖励未领取，请尽快领取！</t>
+  </si>
+  <si>
+    <t>【幸运夺宝】中奖奖励</t>
+  </si>
+  <si>
+    <t>恭喜您在【幸运夺宝】活动中中奖了，赢得以下奖励，请尽快领取！</t>
+  </si>
+  <si>
+    <t>【每日充值】进度礼包奖励</t>
+  </si>
+  <si>
+    <t>您在【每日充值】活动中达到了进度礼包的领取条件，【每日充值】重置后还有未领取的奖励，请尽快领取以下奖励！</t>
+  </si>
+  <si>
+    <t>积分大奖排行奖励-每周榜</t>
+  </si>
+  <si>
+    <t>您在【积分大奖】活动中【第d%期】的周榜排行榜中获得第d%名，请尽快领取以下奖励!</t>
+  </si>
+  <si>
     <t>您在【积分大奖】活动中【第d%期】的周榜排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
-  </si>
-  <si>
-    <t>积分大奖排行奖励-月总榜</t>
-  </si>
-  <si>
-    <t>您在【积分大奖】活动中【第d%期】的月排行榜中获得第d%名，请尽快领取以下奖励!</t>
-  </si>
-  <si>
-    <t>您在【积分大奖】活动中【第d%期】的月排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
-  </si>
-  <si>
-    <t>分享推广-周榜奖励结算发邮件</t>
-  </si>
-  <si>
-    <t>您在【分享推广】活动中周榜排名第d%名，请尽快领取以下奖励!</t>
-  </si>
-  <si>
-    <t>储钱罐-未领奖励到期发邮件</t>
-  </si>
-  <si>
-    <t>您在【储钱罐】活动中购买了一个储钱罐，储钱罐被重置后还有未领取的奖励，请尽快领取以下奖励!</t>
-  </si>
-  <si>
-    <t>[ google绑定 ]奖励</t>
-  </si>
-  <si>
-    <t>您绑定了 Google账号，免费获得 5,200金币，请尽快领取金币奖励!</t>
-  </si>
-  <si>
-    <t>[ facebook绑定 ]奖励</t>
-  </si>
-  <si>
-    <t>您绑定了 facebook账号，免费获得 5,200金金币，请尽快领取金币奖励!</t>
-  </si>
-  <si>
-    <t>[ 手机绑定 ]奖励</t>
-  </si>
-  <si>
-    <t>您绑定了 手机号码，免费获得 5,200金金币，请尽快领取金币奖励!</t>
-  </si>
-  <si>
-    <t>[ Apple绑定 ]奖励</t>
-  </si>
-  <si>
-    <t>您绑定了 Apple账号，免费获得 5,200金金币，请尽快领取金币奖励!</t>
-  </si>
-  <si>
-    <t>房间销毁返还钻石</t>
-  </si>
-  <si>
-    <t>您的【%s】牌局在%s被撤销，现在已经返回游戏中的底庄金额，请尽快领取！</t>
-  </si>
-  <si>
-    <t>[ VIP充值返利 ]金币</t>
-  </si>
-  <si>
-    <t>您在【商城-金币】充值$%s，由于您是VIP%s 充值返利加成%s 额外将获得金币%s ，请尽快领取以下返利!</t>
-  </si>
-  <si>
-    <t>[ VIP充值返利 ]钻石</t>
-  </si>
-  <si>
-    <t>您在【商城-钻石】充值$%s，由于您是VIP%s 充值返利加成%s 额外将获得钻石%s ，请尽快领取以下返利!</t>
-  </si>
-  <si>
-    <t>[ VIP充值返利 ]摇钱树</t>
-  </si>
-  <si>
-    <t>恭喜，您在【摇钱树】活动中中奖，由于您是VIP%s 中奖返利加成%s  额外将获得金币%s，请尽快领取以下返利!</t>
-  </si>
-  <si>
-    <t>上庄结束返还钻石</t>
-  </si>
-  <si>
-    <t>您在【%s】牌局在%s结束上庄，剩余现在已经返回游戏中的剩余上庄金额，请尽快领取！</t>
-  </si>
-  <si>
-    <t>【积分大奖】进度奖励</t>
-  </si>
-  <si>
-    <t>您在【积分大奖】活动中还有积分进度奖励未领取，请尽快领取！</t>
-  </si>
-  <si>
-    <t>【幸运夺宝】中奖奖励</t>
-  </si>
-  <si>
-    <t>恭喜您在【幸运夺宝】活动中中奖了，赢得以下奖励，请尽快领取！</t>
-  </si>
-  <si>
-    <t>【每日充值】进度礼包奖励</t>
-  </si>
-  <si>
-    <t>您在【每日充值】活动中达到了进度礼包的领取条件，【每日充值】重置后还有未领取的奖励，请尽快领取以下奖励！</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="3.75" style="3" customWidth="1"/>
@@ -1241,7 +1250,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F25" si="0">7*24*60*60</f>
+        <f t="shared" ref="F5:F27" si="0">7*24*60*60</f>
         <v>604800</v>
       </c>
       <c r="G5" s="3">
@@ -1785,6 +1794,60 @@
       </c>
       <c r="H25" s="3" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="1:8">
+      <c r="A26" s="2">
+        <v>43</v>
+      </c>
+      <c r="B26" s="2">
+        <v>11403</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G26" s="2">
+        <v>11621</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:8">
+      <c r="A27" s="2">
+        <v>44</v>
+      </c>
+      <c r="B27" s="2">
+        <v>11403</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G27" s="2">
+        <v>11622</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -1319,7 +1319,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>11403</v>
+        <v>11623</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>16</v>
@@ -1346,7 +1346,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2">
-        <v>11403</v>
+        <v>11623</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
@@ -1373,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2">
-        <v>11403</v>
+        <v>11625</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>19</v>
@@ -1400,7 +1400,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2">
-        <v>11403</v>
+        <v>11625</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>19</v>
@@ -1801,7 +1801,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="2">
-        <v>11403</v>
+        <v>11624</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>50</v>
@@ -1828,7 +1828,7 @@
         <v>44</v>
       </c>
       <c r="B27" s="2">
-        <v>11403</v>
+        <v>11624</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>50</v>

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="mail" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -188,6 +188,12 @@
   </si>
   <si>
     <t>您在【积分大奖】活动中【第d%期】的周榜排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
+  </si>
+  <si>
+    <t>每日分享奖励</t>
+  </si>
+  <si>
+    <t>感谢您参与分享有礼活动，请尽快领取金币奖励!</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1155,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="3.75" style="3" customWidth="1"/>
@@ -1250,7 +1256,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F27" si="0">7*24*60*60</f>
+        <f t="shared" ref="F5:F28" si="0">7*24*60*60</f>
         <v>604800</v>
       </c>
       <c r="G5" s="3">
@@ -1848,6 +1854,33 @@
       </c>
       <c r="H27" s="2" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="3">
+        <v>45</v>
+      </c>
+      <c r="B28" s="3">
+        <v>11626</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G28" s="3">
+        <v>11627</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="mail" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="53">
   <si>
     <t>id</t>
   </si>
@@ -188,12 +188,6 @@
   </si>
   <si>
     <t>您在【积分大奖】活动中【第d%期】的周榜排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
-  </si>
-  <si>
-    <t>每日分享奖励</t>
-  </si>
-  <si>
-    <t>感谢您参与分享有礼活动，请尽快领取金币奖励!</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="3.75" style="3" customWidth="1"/>
@@ -1256,7 +1250,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F28" si="0">7*24*60*60</f>
+        <f t="shared" ref="F5:F27" si="0">7*24*60*60</f>
         <v>604800</v>
       </c>
       <c r="G5" s="3">
@@ -1854,33 +1848,6 @@
       </c>
       <c r="H27" s="2" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="3">
-        <v>45</v>
-      </c>
-      <c r="B28" s="3">
-        <v>11626</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D28" s="2">
-        <v>11008</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="2">
-        <f t="shared" si="0"/>
-        <v>604800</v>
-      </c>
-      <c r="G28" s="3">
-        <v>11627</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="mail" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="61">
   <si>
     <t>id</t>
   </si>
@@ -194,6 +194,24 @@
   </si>
   <si>
     <t>感谢您参与分享有礼活动，请尽快领取金币奖励!</t>
+  </si>
+  <si>
+    <t>七日连充·返利挑战奖励</t>
+  </si>
+  <si>
+    <t>您在【七日连充·返利挑战】活动中已完成连充挑战，赢得以下奖励，请尽快领取！</t>
+  </si>
+  <si>
+    <t>累计福利每日奖励</t>
+  </si>
+  <si>
+    <t>您在【累计福利】活动中已完成每日任务挑战，赢得以下奖励，请尽快领取！</t>
+  </si>
+  <si>
+    <t>累计福利累计奖励</t>
+  </si>
+  <si>
+    <t>您在【累计福利】活动中已完成累计任务挑战，赢得以下奖励，请尽快领取！</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="3.75" style="3" customWidth="1"/>
@@ -1256,7 +1274,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F28" si="0">7*24*60*60</f>
+        <f t="shared" ref="F5:F31" si="0">7*24*60*60</f>
         <v>604800</v>
       </c>
       <c r="G5" s="3">
@@ -1881,6 +1899,87 @@
       </c>
       <c r="H28" s="2" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="3">
+        <v>46</v>
+      </c>
+      <c r="B29" s="3">
+        <v>11628</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G29" s="3">
+        <v>11631</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="3">
+        <v>47</v>
+      </c>
+      <c r="B30" s="3">
+        <v>11629</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G30" s="3">
+        <v>11632</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="3">
+        <v>48</v>
+      </c>
+      <c r="B31" s="3">
+        <v>11630</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G31" s="3">
+        <v>11633</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/mail.xlsx
+++ b/poker/resources/sample/mail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="mail" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="61">
   <si>
     <t>id</t>
   </si>
@@ -188,6 +188,30 @@
   </si>
   <si>
     <t>您在【积分大奖】活动中【第d%期】的周榜排行榜中获得第d%名，请尽快前往积分大奖活动界面“排行榜历史”查看！</t>
+  </si>
+  <si>
+    <t>每日分享奖励</t>
+  </si>
+  <si>
+    <t>感谢您参与分享有礼活动，请尽快领取金币奖励!</t>
+  </si>
+  <si>
+    <t>七日连充·返利挑战奖励</t>
+  </si>
+  <si>
+    <t>您在【七日连充·返利挑战】活动中已完成连充挑战，赢得以下奖励，请尽快领取！</t>
+  </si>
+  <si>
+    <t>累计福利每日奖励</t>
+  </si>
+  <si>
+    <t>您在【累计福利】活动中已完成每日任务挑战，赢得以下奖励，请尽快领取！</t>
+  </si>
+  <si>
+    <t>累计福利累计奖励</t>
+  </si>
+  <si>
+    <t>您在【累计福利】活动中已完成累计任务挑战，赢得以下奖励，请尽快领取！</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="3.75" style="3" customWidth="1"/>
@@ -1250,7 +1274,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F27" si="0">7*24*60*60</f>
+        <f t="shared" ref="F5:F31" si="0">7*24*60*60</f>
         <v>604800</v>
       </c>
       <c r="G5" s="3">
@@ -1848,6 +1872,114 @@
       </c>
       <c r="H27" s="2" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="3">
+        <v>45</v>
+      </c>
+      <c r="B28" s="3">
+        <v>11626</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G28" s="3">
+        <v>11627</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="3">
+        <v>46</v>
+      </c>
+      <c r="B29" s="3">
+        <v>11628</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G29" s="3">
+        <v>11631</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="3">
+        <v>47</v>
+      </c>
+      <c r="B30" s="3">
+        <v>11629</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G30" s="3">
+        <v>11632</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="3">
+        <v>48</v>
+      </c>
+      <c r="B31" s="3">
+        <v>11630</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="2">
+        <v>11008</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="2">
+        <f t="shared" si="0"/>
+        <v>604800</v>
+      </c>
+      <c r="G31" s="3">
+        <v>11633</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
